--- a/data/nzd0099/nzd0099.xlsx
+++ b/data/nzd0099/nzd0099.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G306"/>
+  <dimension ref="A1:G307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8698,6 +8698,33 @@
       <c r="G306" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>392.09</v>
+      </c>
+      <c r="C307" t="n">
+        <v>379.18</v>
+      </c>
+      <c r="D307" t="n">
+        <v>384.23</v>
+      </c>
+      <c r="E307" t="n">
+        <v>384.1</v>
+      </c>
+      <c r="F307" t="n">
+        <v>381.12</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11955,6 +11982,16 @@
       </c>
       <c r="B324" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -12123,28 +12160,28 @@
         <v>0.1268</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1557831109497046</v>
+        <v>0.1527975009860452</v>
       </c>
       <c r="J2" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K2" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05627207756043451</v>
+        <v>0.05440443882830703</v>
       </c>
       <c r="M2" t="n">
-        <v>3.748288582365726</v>
+        <v>3.750658443891178</v>
       </c>
       <c r="N2" t="n">
-        <v>21.41271932669219</v>
+        <v>21.4160151767468</v>
       </c>
       <c r="O2" t="n">
-        <v>4.627387959388341</v>
+        <v>4.627744069927247</v>
       </c>
       <c r="P2" t="n">
-        <v>392.7510607411532</v>
+        <v>392.7837287350756</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12201,28 +12238,28 @@
         <v>0.1098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1499251694361998</v>
+        <v>0.1450087650589355</v>
       </c>
       <c r="J3" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K3" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07768513407293165</v>
+        <v>0.07252025508324156</v>
       </c>
       <c r="M3" t="n">
-        <v>2.785576064997598</v>
+        <v>2.800126941931483</v>
       </c>
       <c r="N3" t="n">
-        <v>14.04001623959849</v>
+        <v>14.19281991039382</v>
       </c>
       <c r="O3" t="n">
-        <v>3.747000966052516</v>
+        <v>3.767335916850769</v>
       </c>
       <c r="P3" t="n">
-        <v>383.0723466284737</v>
+        <v>383.1261410189907</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12279,28 +12316,28 @@
         <v>0.1394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1318336107775202</v>
+        <v>0.1308859364071036</v>
       </c>
       <c r="J4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K4" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07277677173311758</v>
+        <v>0.07219425427283643</v>
       </c>
       <c r="M4" t="n">
-        <v>2.720497211976999</v>
+        <v>2.71652800636258</v>
       </c>
       <c r="N4" t="n">
-        <v>11.64986879839715</v>
+        <v>11.61917961171048</v>
       </c>
       <c r="O4" t="n">
-        <v>3.413190413439771</v>
+        <v>3.408691774231059</v>
       </c>
       <c r="P4" t="n">
-        <v>382.2712453072008</v>
+        <v>382.2816145854891</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12357,28 +12394,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1111890921764599</v>
+        <v>0.1096581143024495</v>
       </c>
       <c r="J5" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K5" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05371381347912851</v>
+        <v>0.05255592490334393</v>
       </c>
       <c r="M5" t="n">
-        <v>2.48332736893745</v>
+        <v>2.483324666133646</v>
       </c>
       <c r="N5" t="n">
-        <v>11.45877275762942</v>
+        <v>11.44059260914329</v>
       </c>
       <c r="O5" t="n">
-        <v>3.385080908579501</v>
+        <v>3.382394508206175</v>
       </c>
       <c r="P5" t="n">
-        <v>383.6196660426671</v>
+        <v>383.6364177203786</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12435,28 +12472,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1049485079196354</v>
+        <v>0.1023588528675334</v>
       </c>
       <c r="J6" t="n">
+        <v>306</v>
+      </c>
+      <c r="K6" t="n">
         <v>305</v>
       </c>
-      <c r="K6" t="n">
-        <v>304</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.04399744500125191</v>
+        <v>0.04202459725056851</v>
       </c>
       <c r="M6" t="n">
-        <v>2.836639432022863</v>
+        <v>2.841341846405335</v>
       </c>
       <c r="N6" t="n">
-        <v>12.51533665721628</v>
+        <v>12.52902010589116</v>
       </c>
       <c r="O6" t="n">
-        <v>3.537702171921244</v>
+        <v>3.539635589420351</v>
       </c>
       <c r="P6" t="n">
-        <v>382.4655268847119</v>
+        <v>382.4939940203702</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12494,7 +12531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G306"/>
+  <dimension ref="A1:G307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23815,6 +23852,43 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>-35.714143379307124,174.53155738637903</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>-35.71456734643823,174.5322998181085</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>-35.71481722506455,174.5331343982321</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-35.71507745947807,174.53395184632794</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-35.715281046081415,174.53479986854146</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0099/nzd0099.xlsx
+++ b/data/nzd0099/nzd0099.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G307"/>
+  <dimension ref="A1:G308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8723,6 +8723,33 @@
         <v>381.12</v>
       </c>
       <c r="G307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>393.29</v>
+      </c>
+      <c r="C308" t="n">
+        <v>380.66</v>
+      </c>
+      <c r="D308" t="n">
+        <v>385.22</v>
+      </c>
+      <c r="E308" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="F308" t="n">
+        <v>382.19</v>
+      </c>
+      <c r="G308" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8739,7 +8766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B325"/>
+  <dimension ref="A1:B326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11992,6 +12019,16 @@
       </c>
       <c r="B325" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -12160,28 +12197,28 @@
         <v>0.1268</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1527975009860452</v>
+        <v>0.150587778128302</v>
       </c>
       <c r="J2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05440443882830703</v>
+        <v>0.05315349614685883</v>
       </c>
       <c r="M2" t="n">
-        <v>3.750658443891178</v>
+        <v>3.749142942103078</v>
       </c>
       <c r="N2" t="n">
-        <v>21.4160151767468</v>
+        <v>21.38634864888801</v>
       </c>
       <c r="O2" t="n">
-        <v>4.627744069927247</v>
+        <v>4.62453766866354</v>
       </c>
       <c r="P2" t="n">
-        <v>392.7837287350756</v>
+        <v>392.8080057604318</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12238,28 +12275,28 @@
         <v>0.1098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1450087650589355</v>
+        <v>0.1410635463077119</v>
       </c>
       <c r="J3" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K3" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07252025508324156</v>
+        <v>0.06873159009852225</v>
       </c>
       <c r="M3" t="n">
-        <v>2.800126941931483</v>
+        <v>2.810201516274233</v>
       </c>
       <c r="N3" t="n">
-        <v>14.19281991039382</v>
+        <v>14.27438882057556</v>
       </c>
       <c r="O3" t="n">
-        <v>3.767335916850769</v>
+        <v>3.778146214822232</v>
       </c>
       <c r="P3" t="n">
-        <v>383.1261410189907</v>
+        <v>383.1694849955096</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12316,28 +12353,28 @@
         <v>0.1394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1308859364071036</v>
+        <v>0.1305648264459767</v>
       </c>
       <c r="J4" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K4" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07219425427283643</v>
+        <v>0.07229086299181786</v>
       </c>
       <c r="M4" t="n">
-        <v>2.71652800636258</v>
+        <v>2.709326636732882</v>
       </c>
       <c r="N4" t="n">
-        <v>11.61917961171048</v>
+        <v>11.58217875345632</v>
       </c>
       <c r="O4" t="n">
-        <v>3.408691774231059</v>
+        <v>3.403260018490553</v>
       </c>
       <c r="P4" t="n">
-        <v>382.2816145854891</v>
+        <v>382.2851424462979</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12394,28 +12431,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1096581143024495</v>
+        <v>0.10876102382598</v>
       </c>
       <c r="J5" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K5" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05255592490334393</v>
+        <v>0.05203154809677601</v>
       </c>
       <c r="M5" t="n">
-        <v>2.483324666133646</v>
+        <v>2.479942053754334</v>
       </c>
       <c r="N5" t="n">
-        <v>11.44059260914329</v>
+        <v>11.40993467928827</v>
       </c>
       <c r="O5" t="n">
-        <v>3.382394508206175</v>
+        <v>3.377859481874323</v>
       </c>
       <c r="P5" t="n">
-        <v>383.6364177203786</v>
+        <v>383.6462735664037</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12472,28 +12509,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1023588528675334</v>
+        <v>0.100467510343693</v>
       </c>
       <c r="J6" t="n">
+        <v>307</v>
+      </c>
+      <c r="K6" t="n">
         <v>306</v>
       </c>
-      <c r="K6" t="n">
-        <v>305</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.04202459725056851</v>
+        <v>0.04070830669639469</v>
       </c>
       <c r="M6" t="n">
-        <v>2.841341846405335</v>
+        <v>2.842406550555274</v>
       </c>
       <c r="N6" t="n">
-        <v>12.52902010589116</v>
+        <v>12.5172283527147</v>
       </c>
       <c r="O6" t="n">
-        <v>3.539635589420351</v>
+        <v>3.537969523994618</v>
       </c>
       <c r="P6" t="n">
-        <v>382.4939940203702</v>
+        <v>382.5148694491275</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12531,7 +12568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G307"/>
+  <dimension ref="A1:G308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23889,6 +23926,43 @@
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>-35.71413361533288,174.531563094891</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>-35.71455519643192,174.53230657451155</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>-35.71480895124021,174.53313849875548</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-35.71506885073135,174.53395512414036</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-35.7152716784561,174.53480268557368</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0099/nzd0099.xlsx
+++ b/data/nzd0099/nzd0099.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G308"/>
+  <dimension ref="A1:G310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8750,6 +8750,60 @@
         <v>382.19</v>
       </c>
       <c r="G308" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>396.3</v>
+      </c>
+      <c r="C309" t="n">
+        <v>382.97</v>
+      </c>
+      <c r="D309" t="n">
+        <v>387.33</v>
+      </c>
+      <c r="E309" t="n">
+        <v>386.68</v>
+      </c>
+      <c r="F309" t="n">
+        <v>384.2</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>393.36</v>
+      </c>
+      <c r="C310" t="n">
+        <v>379.76</v>
+      </c>
+      <c r="D310" t="n">
+        <v>384.83</v>
+      </c>
+      <c r="E310" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="F310" t="n">
+        <v>384.03</v>
+      </c>
+      <c r="G310" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8766,7 +8820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B326"/>
+  <dimension ref="A1:B328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12029,6 +12083,26 @@
       </c>
       <c r="B326" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -12197,28 +12271,28 @@
         <v>0.1268</v>
       </c>
       <c r="I2" t="n">
-        <v>0.150587778128302</v>
+        <v>0.1480857455039928</v>
       </c>
       <c r="J2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05315349614685883</v>
+        <v>0.05205038108707638</v>
       </c>
       <c r="M2" t="n">
-        <v>3.749142942103078</v>
+        <v>3.736604303932056</v>
       </c>
       <c r="N2" t="n">
-        <v>21.38634864888801</v>
+        <v>21.28695857765861</v>
       </c>
       <c r="O2" t="n">
-        <v>4.62453766866354</v>
+        <v>4.613779207727501</v>
       </c>
       <c r="P2" t="n">
-        <v>392.8080057604318</v>
+        <v>392.8358147567526</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12275,28 +12349,28 @@
         <v>0.1098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1410635463077119</v>
+        <v>0.1340627921487351</v>
       </c>
       <c r="J3" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K3" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06873159009852225</v>
+        <v>0.06239508454668918</v>
       </c>
       <c r="M3" t="n">
-        <v>2.810201516274233</v>
+        <v>2.825845967123012</v>
       </c>
       <c r="N3" t="n">
-        <v>14.27438882057556</v>
+        <v>14.39500362999198</v>
       </c>
       <c r="O3" t="n">
-        <v>3.778146214822232</v>
+        <v>3.794074805534544</v>
       </c>
       <c r="P3" t="n">
-        <v>383.1694849955096</v>
+        <v>383.2472610030461</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12353,28 +12427,28 @@
         <v>0.1394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1305648264459767</v>
+        <v>0.1309662804878786</v>
       </c>
       <c r="J4" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K4" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07229086299181786</v>
+        <v>0.07353550471185777</v>
       </c>
       <c r="M4" t="n">
-        <v>2.709326636732882</v>
+        <v>2.699908993286965</v>
       </c>
       <c r="N4" t="n">
-        <v>11.58217875345632</v>
+        <v>11.51798345202631</v>
       </c>
       <c r="O4" t="n">
-        <v>3.403260018490553</v>
+        <v>3.393815471121892</v>
       </c>
       <c r="P4" t="n">
-        <v>382.2851424462979</v>
+        <v>382.2807007941861</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12431,28 +12505,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.10876102382598</v>
+        <v>0.106812866579067</v>
       </c>
       <c r="J5" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K5" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05203154809677601</v>
+        <v>0.05076910643321542</v>
       </c>
       <c r="M5" t="n">
-        <v>2.479942053754334</v>
+        <v>2.474993522438991</v>
       </c>
       <c r="N5" t="n">
-        <v>11.40993467928827</v>
+        <v>11.36960157491682</v>
       </c>
       <c r="O5" t="n">
-        <v>3.377859481874323</v>
+        <v>3.37188398004985</v>
       </c>
       <c r="P5" t="n">
-        <v>383.6462735664037</v>
+        <v>383.6679338557129</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12509,28 +12583,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.100467510343693</v>
+        <v>0.09910608454585616</v>
       </c>
       <c r="J6" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K6" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04070830669639469</v>
+        <v>0.04013988231214949</v>
       </c>
       <c r="M6" t="n">
-        <v>2.842406550555274</v>
+        <v>2.831175585110142</v>
       </c>
       <c r="N6" t="n">
-        <v>12.5172283527147</v>
+        <v>12.44336712219518</v>
       </c>
       <c r="O6" t="n">
-        <v>3.537969523994618</v>
+        <v>3.527515715371822</v>
       </c>
       <c r="P6" t="n">
-        <v>382.5148694491275</v>
+        <v>382.5300609207391</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12568,7 +12642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G308"/>
+  <dimension ref="A1:G310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23963,6 +24037,80 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-35.7141091240297,174.53157741373587</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-35.714536232570026,174.53231711997452</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-35.714791317129304,174.53314723825207</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-35.715055248911376,174.5339603030826</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-35.715254081328005,174.53480797738024</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-35.71413304576771,174.53156342788748</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-35.71456258494932,174.5323024658883</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-35.714812210625574,174.53313688339787</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-35.71508426038791,174.53394925685564</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-35.71525556964234,174.5348075298146</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0099/nzd0099.xlsx
+++ b/data/nzd0099/nzd0099.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G310"/>
+  <dimension ref="A1:G312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8806,6 +8806,60 @@
       <c r="G310" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>394.12</v>
+      </c>
+      <c r="C311" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="D311" t="n">
+        <v>385.09</v>
+      </c>
+      <c r="E311" t="n">
+        <v>384.55</v>
+      </c>
+      <c r="F311" t="n">
+        <v>384.24</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>392.13</v>
+      </c>
+      <c r="C312" t="n">
+        <v>380.58</v>
+      </c>
+      <c r="D312" t="n">
+        <v>384.34</v>
+      </c>
+      <c r="E312" t="n">
+        <v>383</v>
+      </c>
+      <c r="F312" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12103,6 +12157,26 @@
       </c>
       <c r="B328" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -12271,28 +12345,28 @@
         <v>0.1268</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1480857455039928</v>
+        <v>0.1435418424972556</v>
       </c>
       <c r="J2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05205038108707638</v>
+        <v>0.04946928867992273</v>
       </c>
       <c r="M2" t="n">
-        <v>3.736604303932056</v>
+        <v>3.733616240447824</v>
       </c>
       <c r="N2" t="n">
-        <v>21.28695857765861</v>
+        <v>21.24082145184999</v>
       </c>
       <c r="O2" t="n">
-        <v>4.613779207727501</v>
+        <v>4.60877656779432</v>
       </c>
       <c r="P2" t="n">
-        <v>392.8358147567526</v>
+        <v>392.8864425524686</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12349,28 +12423,28 @@
         <v>0.1098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1340627921487351</v>
+        <v>0.1258839740732214</v>
       </c>
       <c r="J3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K3" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06239508454668918</v>
+        <v>0.05511155542851121</v>
       </c>
       <c r="M3" t="n">
-        <v>2.825845967123012</v>
+        <v>2.847489397863212</v>
       </c>
       <c r="N3" t="n">
-        <v>14.39500362999198</v>
+        <v>14.57681180281863</v>
       </c>
       <c r="O3" t="n">
-        <v>3.794074805534544</v>
+        <v>3.817959114869963</v>
       </c>
       <c r="P3" t="n">
-        <v>383.2472610030461</v>
+        <v>383.338359725245</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12427,28 +12501,28 @@
         <v>0.1394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1309662804878786</v>
+        <v>0.1296494327445372</v>
       </c>
       <c r="J4" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K4" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07353550471185777</v>
+        <v>0.07300056559177337</v>
       </c>
       <c r="M4" t="n">
-        <v>2.699908993286965</v>
+        <v>2.689134859272361</v>
       </c>
       <c r="N4" t="n">
-        <v>11.51798345202631</v>
+        <v>11.45191916222663</v>
       </c>
       <c r="O4" t="n">
-        <v>3.393815471121892</v>
+        <v>3.384068433443187</v>
       </c>
       <c r="P4" t="n">
-        <v>382.2807007941861</v>
+        <v>382.295374226499</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12505,28 +12579,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.106812866579067</v>
+        <v>0.1034079966209794</v>
       </c>
       <c r="J5" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K5" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05076910643321542</v>
+        <v>0.04812415217649701</v>
       </c>
       <c r="M5" t="n">
-        <v>2.474993522438991</v>
+        <v>2.476748986118953</v>
       </c>
       <c r="N5" t="n">
-        <v>11.36960157491682</v>
+        <v>11.34773675494418</v>
       </c>
       <c r="O5" t="n">
-        <v>3.37188398004985</v>
+        <v>3.368640193749427</v>
       </c>
       <c r="P5" t="n">
-        <v>383.6679338557129</v>
+        <v>383.7058710468119</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12583,28 +12657,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09910608454585616</v>
+        <v>0.0974699517069461</v>
       </c>
       <c r="J6" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K6" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04013988231214949</v>
+        <v>0.03933125729101905</v>
       </c>
       <c r="M6" t="n">
-        <v>2.831175585110142</v>
+        <v>2.821478032882467</v>
       </c>
       <c r="N6" t="n">
-        <v>12.44336712219518</v>
+        <v>12.37486779531404</v>
       </c>
       <c r="O6" t="n">
-        <v>3.527515715371822</v>
+        <v>3.51779302906155</v>
       </c>
       <c r="P6" t="n">
-        <v>382.5300609207391</v>
+        <v>382.5483746022015</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12642,7 +12716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G310"/>
+  <dimension ref="A1:G312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24111,6 +24185,80 @@
         </is>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-35.71412686191721,174.53156704327765</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-35.714561435624404,174.53230310500751</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-35.714810037702,174.53313796030295</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-35.71507358554205,174.5339533213436</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-35.7152537311364,174.5348080826898</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>-35.71414305384133,174.53155757666278</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>-35.71455585318903,174.53230620930063</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>-35.71481630575074,174.53313485384584</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-35.71508692909936,174.53394824073348</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-35.71526029722901,174.53480610813537</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0099/nzd0099.xlsx
+++ b/data/nzd0099/nzd0099.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G312"/>
+  <dimension ref="A1:G313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8858,6 +8858,33 @@
         <v>383.49</v>
       </c>
       <c r="G312" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>394.11</v>
+      </c>
+      <c r="C313" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="D313" t="n">
+        <v>384.01</v>
+      </c>
+      <c r="E313" t="n">
+        <v>385.1</v>
+      </c>
+      <c r="F313" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="G313" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -8874,7 +8901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B330"/>
+  <dimension ref="A1:B331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12177,6 +12204,16 @@
       </c>
       <c r="B330" t="n">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -12345,28 +12382,28 @@
         <v>0.1268</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1435418424972556</v>
+        <v>0.1419139497674132</v>
       </c>
       <c r="J2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04946928867992273</v>
+        <v>0.04866150768247601</v>
       </c>
       <c r="M2" t="n">
-        <v>3.733616240447824</v>
+        <v>3.729083557886332</v>
       </c>
       <c r="N2" t="n">
-        <v>21.24082145184999</v>
+        <v>21.19452750174905</v>
       </c>
       <c r="O2" t="n">
-        <v>4.60877656779432</v>
+        <v>4.603751459597818</v>
       </c>
       <c r="P2" t="n">
-        <v>392.8864425524686</v>
+        <v>392.9046637242152</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -12423,28 +12460,28 @@
         <v>0.1098</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1258839740732214</v>
+        <v>0.1222704480482315</v>
       </c>
       <c r="J3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05511155542851121</v>
+        <v>0.05211442725789928</v>
       </c>
       <c r="M3" t="n">
-        <v>2.847489397863212</v>
+        <v>2.856244850657149</v>
       </c>
       <c r="N3" t="n">
-        <v>14.57681180281863</v>
+        <v>14.63743591303532</v>
       </c>
       <c r="O3" t="n">
-        <v>3.817959114869963</v>
+        <v>3.825890211837673</v>
       </c>
       <c r="P3" t="n">
-        <v>383.338359725245</v>
+        <v>383.3788062958976</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12501,28 +12538,28 @@
         <v>0.1394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1296494327445372</v>
+        <v>0.128554802392502</v>
       </c>
       <c r="J4" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K4" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07300056559177337</v>
+        <v>0.07223998538348464</v>
       </c>
       <c r="M4" t="n">
-        <v>2.689134859272361</v>
+        <v>2.685946388228662</v>
       </c>
       <c r="N4" t="n">
-        <v>11.45191916222663</v>
+        <v>11.42506467452477</v>
       </c>
       <c r="O4" t="n">
-        <v>3.384068433443187</v>
+        <v>3.380098323203745</v>
       </c>
       <c r="P4" t="n">
-        <v>382.295374226499</v>
+        <v>382.3076265372795</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12579,28 +12616,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1034079966209794</v>
+        <v>0.1025510000012229</v>
       </c>
       <c r="J5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04812415217649701</v>
+        <v>0.0476385839831629</v>
       </c>
       <c r="M5" t="n">
-        <v>2.476748986118953</v>
+        <v>2.473199496746276</v>
       </c>
       <c r="N5" t="n">
-        <v>11.34773675494418</v>
+        <v>11.3174035700135</v>
       </c>
       <c r="O5" t="n">
-        <v>3.368640193749427</v>
+        <v>3.364134891768388</v>
       </c>
       <c r="P5" t="n">
-        <v>383.7058710468119</v>
+        <v>383.7154634986416</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12657,28 +12694,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0974699517069461</v>
+        <v>0.09762239993200571</v>
       </c>
       <c r="J6" t="n">
+        <v>312</v>
+      </c>
+      <c r="K6" t="n">
         <v>311</v>
       </c>
-      <c r="K6" t="n">
-        <v>310</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03933125729101905</v>
+        <v>0.03969739964103958</v>
       </c>
       <c r="M6" t="n">
-        <v>2.821478032882467</v>
+        <v>2.813172208112532</v>
       </c>
       <c r="N6" t="n">
-        <v>12.37486779531404</v>
+        <v>12.33526682721719</v>
       </c>
       <c r="O6" t="n">
-        <v>3.51779302906155</v>
+        <v>3.512159852173188</v>
       </c>
       <c r="P6" t="n">
-        <v>382.5483746022015</v>
+        <v>382.5466604194727</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -12716,7 +12753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G312"/>
+  <dimension ref="A1:G313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24259,6 +24296,43 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>-35.71412694328367,174.53156699570673</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-35.71455330825524,174.53230762449292</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>-35.71481906369216,174.53313348700456</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-35.71506885073135,174.53395512414036</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-35.71524357557979,174.5348111366667</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
